--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\demo 1\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D806DE9-5050-44C4-A05D-A7C192DA71B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54AA14E-E8E3-48FB-BF4F-E380AED746AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,6 +214,12 @@
   </si>
   <si>
     <t>High</t>
+  </si>
+  <si>
+    <t>2026-08--23</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -1215,69 +1221,135 @@
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="14">
+        <v>480</v>
+      </c>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14">
+        <v>210</v>
+      </c>
+      <c r="E11" s="14">
+        <v>90</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>600</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>30</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B12" s="14">
+        <v>540</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>210</v>
+      </c>
+      <c r="E12" s="14">
+        <v>90</v>
+      </c>
+      <c r="F12" s="14">
+        <v>200</v>
+      </c>
+      <c r="G12" s="14">
+        <v>4</v>
+      </c>
+      <c r="H12" s="14">
+        <v>300</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>70</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B13" s="14">
+        <v>480</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>210</v>
+      </c>
+      <c r="E13" s="14">
+        <v>90</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>200</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>80</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\demo 1\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54AA14E-E8E3-48FB-BF4F-E380AED746AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8224101-4674-4ABD-9501-851C36155741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -220,6 +220,12 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
   </si>
 </sst>
 </file>
@@ -1353,135 +1359,267 @@
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B14" s="14">
+        <v>540</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>180</v>
+      </c>
+      <c r="E14" s="14">
+        <v>90</v>
+      </c>
+      <c r="F14" s="14">
+        <v>350</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>200</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>50</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B15" s="14">
+        <v>480</v>
+      </c>
+      <c r="C15" s="14">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>180</v>
+      </c>
+      <c r="E15" s="14">
+        <v>90</v>
+      </c>
+      <c r="F15" s="14">
+        <v>200</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>300</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B16" s="14">
+        <v>510</v>
+      </c>
+      <c r="C16" s="14">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>180</v>
+      </c>
+      <c r="E16" s="14">
+        <v>90</v>
+      </c>
+      <c r="F16" s="14">
+        <v>250</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
+        <v>300</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>90</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B17" s="14">
+        <v>540</v>
+      </c>
+      <c r="C17" s="14">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
+        <v>240</v>
+      </c>
+      <c r="E17" s="14">
+        <v>120</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>400</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>120</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B18" s="14">
+        <v>600</v>
+      </c>
+      <c r="C18" s="14">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>240</v>
+      </c>
+      <c r="E18" s="14">
+        <v>120</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>300</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>160</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>20</v>
+      </c>
+      <c r="D19" s="14">
+        <v>210</v>
+      </c>
+      <c r="E19" s="14">
+        <v>90</v>
+      </c>
+      <c r="F19" s="14">
+        <v>200</v>
+      </c>
+      <c r="G19" s="14">
+        <v>4</v>
+      </c>
+      <c r="H19" s="14">
+        <v>300</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+        <v>200</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\demo 1\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8224101-4674-4ABD-9501-851C36155741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973464F4-107B-44E9-A74B-17C3BBB52ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1623,25 +1623,47 @@
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B20" s="14">
+        <v>480</v>
+      </c>
+      <c r="C20" s="14">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>210</v>
+      </c>
+      <c r="E20" s="14">
+        <v>90</v>
+      </c>
+      <c r="F20" s="14">
+        <v>350</v>
+      </c>
+      <c r="G20" s="14">
+        <v>7</v>
+      </c>
+      <c r="H20" s="14">
+        <v>200</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+        <v>90</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\demo 1\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973464F4-107B-44E9-A74B-17C3BBB52ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33717F8-F02B-462F-B4AE-7D99443501CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1667,47 +1667,91 @@
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B21" s="14">
+        <v>480</v>
+      </c>
+      <c r="C21" s="14">
+        <v>20</v>
+      </c>
+      <c r="D21" s="14">
+        <v>210</v>
+      </c>
+      <c r="E21" s="14">
+        <v>90</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>200</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+        <v>90</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>240</v>
+      </c>
+      <c r="E22" s="14">
+        <v>90</v>
+      </c>
+      <c r="F22" s="14">
+        <v>200</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>300</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\demo 1\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33717F8-F02B-462F-B4AE-7D99443501CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C9B9BD-0BD8-42C0-88BF-6B05A5069063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1755,25 +1755,47 @@
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>240</v>
+      </c>
+      <c r="E23" s="14">
+        <v>90</v>
+      </c>
+      <c r="F23" s="14">
+        <v>250</v>
+      </c>
+      <c r="G23" s="14">
+        <v>5</v>
+      </c>
+      <c r="H23" s="14">
+        <v>300</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+        <v>120</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\demo 1\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C9B9BD-0BD8-42C0-88BF-6B05A5069063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D0B88D-1594-4BBD-98F2-6F9435366613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -226,6 +226,9 @@
   </si>
   <si>
     <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1799,47 +1802,91 @@
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B24" s="14">
+        <v>480</v>
+      </c>
+      <c r="C24" s="14">
+        <v>20</v>
+      </c>
+      <c r="D24" s="14">
+        <v>180</v>
+      </c>
+      <c r="E24" s="14">
+        <v>60</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>300</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>400</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B25" s="14">
+        <v>600</v>
+      </c>
+      <c r="C25" s="14">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14">
+        <v>300</v>
+      </c>
+      <c r="E25" s="14">
+        <v>180</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>300</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>40</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\demo 1\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D0B88D-1594-4BBD-98F2-6F9435366613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB07C150-AB71-4D33-A57D-FDABA29FBEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -340,7 +340,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -363,11 +363,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -411,6 +422,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1890,179 +1904,355 @@
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B26" s="14">
+        <v>540</v>
+      </c>
+      <c r="C26" s="14">
+        <v>20</v>
+      </c>
+      <c r="D26" s="14">
+        <v>240</v>
+      </c>
+      <c r="E26" s="14">
+        <v>90</v>
+      </c>
+      <c r="F26" s="14">
+        <v>200</v>
+      </c>
+      <c r="G26" s="14">
+        <v>4</v>
+      </c>
+      <c r="H26" s="14">
+        <v>200</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+        <v>150</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B27" s="14">
+        <v>480</v>
+      </c>
+      <c r="C27" s="14">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>240</v>
+      </c>
+      <c r="E27" s="14">
+        <v>90</v>
+      </c>
+      <c r="F27" s="14">
+        <v>350</v>
+      </c>
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="14">
+        <v>200</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+        <v>60</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="21" t="s">
+        <v>51</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B28" s="14">
+        <v>540</v>
+      </c>
+      <c r="C28" s="14">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>180</v>
+      </c>
+      <c r="E28" s="14">
+        <v>90</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>200</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
+        <v>60</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B29" s="14">
+        <v>480</v>
+      </c>
+      <c r="C29" s="14">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
+        <v>180</v>
+      </c>
+      <c r="E29" s="14">
+        <v>90</v>
+      </c>
+      <c r="F29" s="14">
+        <v>200</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14">
+        <v>200</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+        <v>270</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B30" s="14">
+        <v>480</v>
+      </c>
+      <c r="C30" s="14">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
+        <v>180</v>
+      </c>
+      <c r="E30" s="14">
+        <v>90</v>
+      </c>
+      <c r="F30" s="14">
+        <v>250</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>200</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B31" s="14">
+        <v>540</v>
+      </c>
+      <c r="C31" s="14">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
+        <v>240</v>
+      </c>
+      <c r="E31" s="14">
+        <v>90</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>300</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+        <v>250</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B32" s="14">
+        <v>540</v>
+      </c>
+      <c r="C32" s="14">
+        <v>20</v>
+      </c>
+      <c r="D32" s="14">
+        <v>240</v>
+      </c>
+      <c r="E32" s="14">
+        <v>120</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>300</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B33" s="14">
+        <v>480</v>
+      </c>
+      <c r="C33" s="14">
+        <v>20</v>
+      </c>
+      <c r="D33" s="14">
+        <v>180</v>
+      </c>
+      <c r="E33" s="14">
+        <v>90</v>
+      </c>
+      <c r="F33" s="14">
+        <v>200</v>
+      </c>
+      <c r="G33" s="14">
+        <v>4</v>
+      </c>
+      <c r="H33" s="14">
+        <v>200</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>270</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -10180,11 +10370,11 @@
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L26 L28:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M26 M28:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\demo 1\776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/256b75f619a51fa0/Desktop/demo 1/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB07C150-AB71-4D33-A57D-FDABA29FBEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{AB07C150-AB71-4D33-A57D-FDABA29FBEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F53FD1FF-EAA6-4278-AB5C-F4E7AE90C610}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -419,12 +419,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -908,74 +908,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12621662</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1983,10 +1983,10 @@
       <c r="K27" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L27" s="21" t="s">
+      <c r="L27" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="M27" s="21" t="s">
+      <c r="M27" s="18" t="s">
         <v>51</v>
       </c>
       <c r="N27" s="17"/>
@@ -2256,69 +2256,134 @@
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B34" s="14">
+        <v>480</v>
+      </c>
+      <c r="C34" s="14">
+        <v>20</v>
+      </c>
+      <c r="D34" s="14">
+        <v>180</v>
+      </c>
+      <c r="E34" s="14">
+        <v>90</v>
+      </c>
+      <c r="F34" s="14">
+        <v>250</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>200</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J34" s="15">
+        <v>220</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B35" s="14">
+        <v>480</v>
+      </c>
+      <c r="C35" s="14">
+        <v>20</v>
+      </c>
+      <c r="D35" s="14">
+        <v>180</v>
+      </c>
+      <c r="E35" s="14">
+        <v>90</v>
+      </c>
+      <c r="F35" s="14">
+        <v>300</v>
+      </c>
+      <c r="G35" s="14">
+        <v>6</v>
+      </c>
+      <c r="H35" s="14">
+        <v>200</v>
+      </c>
+      <c r="I35" s="15">
+        <f t="shared" si="0"/>
+        <v>1270</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+        <v>170</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B36" s="14">
+        <v>480</v>
+      </c>
+      <c r="C36" s="14">
+        <v>20</v>
+      </c>
+      <c r="D36" s="14">
+        <v>180</v>
+      </c>
+      <c r="E36" s="14">
+        <v>90</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>200</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
+        <v>270</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
